--- a/InputData/endo-learn/BGSaWC/BAU Global Solar and Wind Cap.xlsx
+++ b/InputData/endo-learn/BGSaWC/BAU Global Solar and Wind Cap.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-us\InputData\endo-learn\BGSaWC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/endo-learn/BGSaWC/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F882FA60-0168-4D4B-BA02-D927D2CFDA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22635" windowHeight="11550"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -17,10 +18,21 @@
     <sheet name="IEA 2017 Wind" sheetId="2" r:id="rId3"/>
     <sheet name="BGSaWC" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -167,7 +179,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#\ ##0"/>
@@ -291,22 +303,22 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
@@ -319,9 +331,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -334,7 +343,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Table Header 2" xfId="2"/>
+    <cellStyle name="Table Header 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -381,7 +390,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1124,19 +1139,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1144,101 +1159,101 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="11">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B8" s="16" t="s">
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" s="17" t="s">
+    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" s="11">
         <v>2017</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1"/>
-    <hyperlink ref="B7" r:id="rId2"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B1">
         <v>2019</v>
       </c>
@@ -1249,7 +1264,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1263,7 +1278,7 @@
         <v>4474</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -1277,7 +1292,7 @@
         <v>2434</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2019</v>
       </c>
@@ -1375,7 +1390,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1384,7 +1399,7 @@
         <v>582000</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:N6" si="0">TREND($B$2:$C$2,$B$1:$C$1,C5)*1000</f>
+        <f t="shared" ref="C6:M6" si="0">TREND($B$2:$C$2,$B$1:$C$1,C5)*1000</f>
         <v>714272.72727276431</v>
       </c>
       <c r="D6">
@@ -1508,7 +1523,7 @@
         <v>4474000</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1517,7 +1532,7 @@
         <v>624000</v>
       </c>
       <c r="C7">
-        <f t="shared" ref="C7:N7" si="2">TREND($B$3:$C$3,$B$1:$C$1,C5)*1000</f>
+        <f t="shared" ref="C7:M7" si="2">TREND($B$3:$C$3,$B$1:$C$1,C5)*1000</f>
         <v>699545.45454544132</v>
       </c>
       <c r="D7">
@@ -1648,21 +1663,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A7:AN22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="9.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="38" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="38" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:40" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:40" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -1784,7 +1799,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>4</v>
       </c>
@@ -1930,7 +1945,7 @@
         <v>2072.8400198583167</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>5</v>
       </c>
@@ -2076,7 +2091,7 @@
         <v>135.57703324231764</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -2229,12 +2244,12 @@
         <v>6.5406414360711082E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:30" ht="19" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>7</v>
       </c>
@@ -2326,7 +2341,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>8</v>
       </c>
@@ -2418,7 +2433,7 @@
         <v>1977.5444351764106</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>9</v>
       </c>
@@ -2515,8 +2530,6 @@
     <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>MOD(ROW(),2)=1</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A21:AD22">
     <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -2527,17 +2540,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AG17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BA17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.3984375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>31</v>
       </c>
@@ -2637,9 +2650,69 @@
       <c r="AG1">
         <v>2050</v>
       </c>
+      <c r="AH1">
+        <v>2051</v>
+      </c>
+      <c r="AI1">
+        <v>2052</v>
+      </c>
+      <c r="AJ1">
+        <v>2053</v>
+      </c>
+      <c r="AK1">
+        <v>2054</v>
+      </c>
+      <c r="AL1">
+        <v>2055</v>
+      </c>
+      <c r="AM1">
+        <v>2056</v>
+      </c>
+      <c r="AN1">
+        <v>2057</v>
+      </c>
+      <c r="AO1">
+        <v>2058</v>
+      </c>
+      <c r="AP1">
+        <v>2059</v>
+      </c>
+      <c r="AQ1">
+        <v>2060</v>
+      </c>
+      <c r="AR1">
+        <v>2061</v>
+      </c>
+      <c r="AS1">
+        <v>2062</v>
+      </c>
+      <c r="AT1">
+        <v>2063</v>
+      </c>
+      <c r="AU1">
+        <v>2064</v>
+      </c>
+      <c r="AV1">
+        <v>2065</v>
+      </c>
+      <c r="AW1">
+        <v>2066</v>
+      </c>
+      <c r="AX1">
+        <v>2067</v>
+      </c>
+      <c r="AY1">
+        <v>2068</v>
+      </c>
+      <c r="AZ1">
+        <v>2069</v>
+      </c>
+      <c r="BA1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B2">
@@ -2738,9 +2811,69 @@
       <c r="AG2">
         <v>0</v>
       </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B3">
@@ -2839,9 +2972,69 @@
       <c r="AG3">
         <v>0</v>
       </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B4">
@@ -2940,9 +3133,69 @@
       <c r="AG4">
         <v>0</v>
       </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B5">
@@ -3041,275 +3294,495 @@
       <c r="AG5">
         <v>0</v>
       </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <f>'Global Renewables Outlook'!B7*(1-'IEA 2017 Wind'!I12)</f>
         <v>607804.03146737406</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="14">
         <f>'Global Renewables Outlook'!C7*(1-'IEA 2017 Wind'!J12)</f>
         <v>681371.59811876004</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <f>'Global Renewables Outlook'!D7*(1-'IEA 2017 Wind'!K12)</f>
         <v>754938.35798369965</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="14">
         <f>'Global Renewables Outlook'!E7*(1-'IEA 2017 Wind'!L12)</f>
         <v>828504.48238323536</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
         <f>'Global Renewables Outlook'!F7*(1-'IEA 2017 Wind'!M12)</f>
         <v>902070.09733831172</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="14">
         <f>'Global Renewables Outlook'!G7*(1-'IEA 2017 Wind'!N12)</f>
         <v>975635.29761384299</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <f>'Global Renewables Outlook'!H7*(1-'IEA 2017 Wind'!O12)</f>
         <v>1049200.1558433597</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="14">
         <f>'Global Renewables Outlook'!I7*(1-'IEA 2017 Wind'!P12)</f>
         <v>1121222.8094770459</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="14">
         <f>'Global Renewables Outlook'!J7*(1-'IEA 2017 Wind'!Q12)</f>
         <v>1193207.4250556889</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="14">
         <f>'Global Renewables Outlook'!K7*(1-'IEA 2017 Wind'!R12)</f>
         <v>1265159.4382497929</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="14">
         <f>'Global Renewables Outlook'!L7*(1-'IEA 2017 Wind'!S12)</f>
         <v>1337083.296137417</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="14">
         <f>'Global Renewables Outlook'!M7*(1-'IEA 2017 Wind'!T12)</f>
         <v>1408982.6721757923</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="14">
         <f>'Global Renewables Outlook'!N7*(1-'IEA 2017 Wind'!U12)</f>
         <v>1454354.0181945674</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="14">
         <f>'Global Renewables Outlook'!O7*(1-'IEA 2017 Wind'!V12)</f>
         <v>1499746.3552090656</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="14">
         <f>'Global Renewables Outlook'!P7*(1-'IEA 2017 Wind'!W12)</f>
         <v>1545157.4640270318</v>
       </c>
-      <c r="Q6" s="15">
+      <c r="Q6" s="14">
         <f>'Global Renewables Outlook'!Q7*(1-'IEA 2017 Wind'!X12)</f>
         <v>1590585.4276282906</v>
       </c>
-      <c r="R6" s="15">
+      <c r="R6" s="14">
         <f>'Global Renewables Outlook'!R7*(1-'IEA 2017 Wind'!Y12)</f>
         <v>1636028.58142701</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="14">
         <f>'Global Renewables Outlook'!S7*(1-'IEA 2017 Wind'!Z12)</f>
         <v>1680197.7520111771</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="14">
         <f>'Global Renewables Outlook'!T7*(1-'IEA 2017 Wind'!AA12)</f>
         <v>1724348.2566176786</v>
       </c>
-      <c r="U6" s="15">
+      <c r="U6" s="14">
         <f>'Global Renewables Outlook'!U7*(1-'IEA 2017 Wind'!AB12)</f>
         <v>1768481.4155999315</v>
       </c>
-      <c r="V6" s="15">
+      <c r="V6" s="14">
         <f>'Global Renewables Outlook'!V7*(1-'IEA 2017 Wind'!AC12)</f>
         <v>1812598.4276515185</v>
       </c>
-      <c r="W6" s="15">
+      <c r="W6" s="14">
         <f>'Global Renewables Outlook'!W7*(1-'IEA 2017 Wind'!AD12)</f>
         <v>1856700.3835031393</v>
       </c>
-      <c r="X6" s="15">
+      <c r="X6" s="14">
         <f>'Global Renewables Outlook'!X7*(1-'IEA 2017 Wind'!AE12)</f>
         <v>1899173.3917596261</v>
       </c>
-      <c r="Y6" s="15">
+      <c r="Y6" s="14">
         <f>'Global Renewables Outlook'!Y7*(1-'IEA 2017 Wind'!AF12)</f>
         <v>1941610.9600069062</v>
       </c>
-      <c r="Z6" s="15">
+      <c r="Z6" s="14">
         <f>'Global Renewables Outlook'!Z7*(1-'IEA 2017 Wind'!AG12)</f>
         <v>1984015.1641012894</v>
       </c>
-      <c r="AA6" s="15">
+      <c r="AA6" s="14">
         <f>'Global Renewables Outlook'!AA7*(1-'IEA 2017 Wind'!AH12)</f>
         <v>2026387.9208827256</v>
       </c>
-      <c r="AB6" s="15">
+      <c r="AB6" s="14">
         <f>'Global Renewables Outlook'!AB7*(1-'IEA 2017 Wind'!AI12)</f>
         <v>2068731.0031150684</v>
       </c>
-      <c r="AC6" s="15">
+      <c r="AC6" s="14">
         <f>'Global Renewables Outlook'!AC7*(1-'IEA 2017 Wind'!AJ12)</f>
         <v>2109832.2301834417</v>
       </c>
-      <c r="AD6" s="15">
+      <c r="AD6" s="14">
         <f>'Global Renewables Outlook'!AD7*(1-'IEA 2017 Wind'!AK12)</f>
         <v>2150994.4197746827</v>
       </c>
-      <c r="AE6" s="15">
+      <c r="AE6" s="14">
         <f>'Global Renewables Outlook'!AE7*(1-'IEA 2017 Wind'!AL12)</f>
         <v>2192212.7308672476</v>
       </c>
-      <c r="AF6" s="15">
+      <c r="AF6" s="14">
         <f>'Global Renewables Outlook'!AF7*(1-'IEA 2017 Wind'!AM12)</f>
         <v>2233482.8217879166</v>
       </c>
-      <c r="AG6" s="15">
+      <c r="AG6" s="14">
         <f>'Global Renewables Outlook'!AG7*(1-'IEA 2017 Wind'!AN12)</f>
         <v>2274800.7874460295</v>
       </c>
+      <c r="AH6">
+        <f>_xlfn.FORECAST.LINEAR(AH1,$B$6:$AG$6,$B$1:$AG$1)</f>
+        <v>2411444.9157484174</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" ref="AI6:BA6" si="0">_xlfn.FORECAST.LINEAR(AI1,$B$6:$AG$6,$B$1:$AG$1)</f>
+        <v>2463701.7682679445</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>2515958.6207874715</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>2568215.4733069986</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>2620472.3258265257</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>2672729.1783460528</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>2724986.0308655798</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>2777242.8833851069</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>2829499.735904634</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>2881756.5884241611</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>2934013.4409436882</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>2986270.2934632152</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>3038527.1459827423</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>3090783.9985022694</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>3143040.8510217965</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>3195297.7035413384</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>3247554.5560608655</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>3299811.4085803926</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>3352068.2610999197</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="0"/>
+        <v>3404325.1136194468</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <f>'Global Renewables Outlook'!B6</f>
         <v>582000</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="14">
         <f>'Global Renewables Outlook'!C6</f>
         <v>714272.72727276431</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <f>'Global Renewables Outlook'!D6</f>
         <v>846545.45454547042</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="14">
         <f>'Global Renewables Outlook'!E6</f>
         <v>978818.18181823473</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <f>'Global Renewables Outlook'!F6</f>
         <v>1111090.9090909408</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="14">
         <f>'Global Renewables Outlook'!G6</f>
         <v>1243363.6363636469</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="14">
         <f>'Global Renewables Outlook'!H6</f>
         <v>1375636.3636364113</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="14">
         <f>'Global Renewables Outlook'!I6</f>
         <v>1507909.0909091174</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="14">
         <f>'Global Renewables Outlook'!J6</f>
         <v>1640181.8181818235</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="14">
         <f>'Global Renewables Outlook'!K6</f>
         <v>1772454.5454545878</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="14">
         <f>'Global Renewables Outlook'!L6</f>
         <v>1904727.2727272939</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="14">
         <f>'Global Renewables Outlook'!M6</f>
         <v>2037000</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="14">
         <f>'Global Renewables Outlook'!N6</f>
         <v>2158849.9999999767</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="14">
         <f>'Global Renewables Outlook'!O6</f>
         <v>2280699.9999999823</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="14">
         <f>'Global Renewables Outlook'!P6</f>
         <v>2402549.9999999884</v>
       </c>
-      <c r="Q7" s="15">
+      <c r="Q7" s="14">
         <f>'Global Renewables Outlook'!Q6</f>
         <v>2524399.9999999944</v>
       </c>
-      <c r="R7" s="15">
+      <c r="R7" s="14">
         <f>'Global Renewables Outlook'!R6</f>
         <v>2646250</v>
       </c>
-      <c r="S7" s="15">
+      <c r="S7" s="14">
         <f>'Global Renewables Outlook'!S6</f>
         <v>2768099.9999999767</v>
       </c>
-      <c r="T7" s="15">
+      <c r="T7" s="14">
         <f>'Global Renewables Outlook'!T6</f>
         <v>2889949.9999999823</v>
       </c>
-      <c r="U7" s="15">
+      <c r="U7" s="14">
         <f>'Global Renewables Outlook'!U6</f>
         <v>3011799.9999999884</v>
       </c>
-      <c r="V7" s="15">
+      <c r="V7" s="14">
         <f>'Global Renewables Outlook'!V6</f>
         <v>3133649.9999999944</v>
       </c>
-      <c r="W7" s="15">
+      <c r="W7" s="14">
         <f>'Global Renewables Outlook'!W6</f>
         <v>3255500</v>
       </c>
-      <c r="X7" s="15">
+      <c r="X7" s="14">
         <f>'Global Renewables Outlook'!X6</f>
         <v>3377349.9999999767</v>
       </c>
-      <c r="Y7" s="15">
+      <c r="Y7" s="14">
         <f>'Global Renewables Outlook'!Y6</f>
         <v>3499199.9999999823</v>
       </c>
-      <c r="Z7" s="15">
+      <c r="Z7" s="14">
         <f>'Global Renewables Outlook'!Z6</f>
         <v>3621049.9999999884</v>
       </c>
-      <c r="AA7" s="15">
+      <c r="AA7" s="14">
         <f>'Global Renewables Outlook'!AA6</f>
         <v>3742899.9999999944</v>
       </c>
-      <c r="AB7" s="15">
+      <c r="AB7" s="14">
         <f>'Global Renewables Outlook'!AB6</f>
         <v>3864750</v>
       </c>
-      <c r="AC7" s="15">
+      <c r="AC7" s="14">
         <f>'Global Renewables Outlook'!AC6</f>
         <v>3986599.9999999767</v>
       </c>
-      <c r="AD7" s="15">
+      <c r="AD7" s="14">
         <f>'Global Renewables Outlook'!AD6</f>
         <v>4108449.9999999823</v>
       </c>
-      <c r="AE7" s="15">
+      <c r="AE7" s="14">
         <f>'Global Renewables Outlook'!AE6</f>
         <v>4230299.9999999888</v>
       </c>
-      <c r="AF7" s="15">
+      <c r="AF7" s="14">
         <f>'Global Renewables Outlook'!AF6</f>
         <v>4352149.9999999944</v>
       </c>
-      <c r="AG7" s="15">
+      <c r="AG7" s="14">
         <f>'Global Renewables Outlook'!AG6</f>
         <v>4474000</v>
       </c>
+      <c r="AH7">
+        <f>_xlfn.FORECAST.LINEAR(AH1,$B$7:$AG$7,$B$1:$AG$1)</f>
+        <v>4624974.7983870804</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" ref="AI7:BA7" si="1">_xlfn.FORECAST.LINEAR(AI1,$B$7:$AG$7,$B$1:$AG$1)</f>
+        <v>4749892.7785923481</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="1"/>
+        <v>4874810.7587976456</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="1"/>
+        <v>4999728.7390029132</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="1"/>
+        <v>5124646.7192081809</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="1"/>
+        <v>5249564.6994134784</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="1"/>
+        <v>5374482.679618746</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="1"/>
+        <v>5499400.6598240137</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="1"/>
+        <v>5624318.6400292814</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="1"/>
+        <v>5749236.6202345788</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="1"/>
+        <v>5874154.6004398465</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="1"/>
+        <v>5999072.5806451142</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="1"/>
+        <v>6123990.5608504117</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="1"/>
+        <v>6248908.5410556793</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="1"/>
+        <v>6373826.521260947</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="1"/>
+        <v>6498744.5014662445</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="1"/>
+        <v>6623662.4816715121</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="1"/>
+        <v>6748580.4618767798</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="1"/>
+        <v>6873498.4420820773</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="1"/>
+        <v>6998416.4222873449</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B8">
@@ -3408,9 +3881,69 @@
       <c r="AG8">
         <v>0</v>
       </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>21</v>
       </c>
       <c r="B9">
@@ -3509,9 +4042,69 @@
       <c r="AG9">
         <v>0</v>
       </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>22</v>
       </c>
       <c r="B10">
@@ -3610,9 +4203,69 @@
       <c r="AG10">
         <v>0</v>
       </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B11">
@@ -3711,9 +4364,69 @@
       <c r="AG11">
         <v>0</v>
       </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B12">
@@ -3812,9 +4525,69 @@
       <c r="AG12">
         <v>0</v>
       </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B13">
@@ -3913,141 +4686,281 @@
       <c r="AG13">
         <v>0</v>
       </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <f>'Global Renewables Outlook'!B7*'IEA 2017 Wind'!I12</f>
         <v>16195.968532625964</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <f>'Global Renewables Outlook'!C7*'IEA 2017 Wind'!J12</f>
         <v>18173.856426681279</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f>'Global Renewables Outlook'!D7*'IEA 2017 Wind'!K12</f>
         <v>20152.551107212112</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <f>'Global Renewables Outlook'!E7*'IEA 2017 Wind'!L12</f>
         <v>22131.881253117648</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
         <f>'Global Renewables Outlook'!F7*'IEA 2017 Wind'!M12</f>
         <v>24111.720843511761</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <f>'Global Renewables Outlook'!G7*'IEA 2017 Wind'!N12</f>
         <v>26091.975113421791</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="14">
         <f>'Global Renewables Outlook'!H7*'IEA 2017 Wind'!O12</f>
         <v>28072.571429375646</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="14">
         <f>'Global Renewables Outlook'!I7*'IEA 2017 Wind'!P12</f>
         <v>31595.372341130736</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="14">
         <f>'Global Renewables Outlook'!J7*'IEA 2017 Wind'!Q12</f>
         <v>35156.211307928854</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="14">
         <f>'Global Renewables Outlook'!K7*'IEA 2017 Wind'!R12</f>
         <v>38749.652659295331</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="14">
         <f>'Global Renewables Outlook'!L7*'IEA 2017 Wind'!S12</f>
         <v>42371.249317112568</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="14">
         <f>'Global Renewables Outlook'!M7*'IEA 2017 Wind'!T12</f>
         <v>46017.327824207787</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="14">
         <f>'Global Renewables Outlook'!N7*'IEA 2017 Wind'!U12</f>
         <v>49595.981805444135</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14" s="14">
         <f>'Global Renewables Outlook'!O7*'IEA 2017 Wind'!V12</f>
         <v>53153.644790943217</v>
       </c>
-      <c r="P14" s="15">
+      <c r="P14" s="14">
         <f>'Global Renewables Outlook'!P7*'IEA 2017 Wind'!W12</f>
         <v>56692.535972973987</v>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q14" s="14">
         <f>'Global Renewables Outlook'!Q7*'IEA 2017 Wind'!X12</f>
         <v>60214.572371712304</v>
       </c>
-      <c r="R14" s="15">
+      <c r="R14" s="14">
         <f>'Global Renewables Outlook'!R7*'IEA 2017 Wind'!Y12</f>
         <v>63721.418572989911</v>
       </c>
-      <c r="S14" s="15">
+      <c r="S14" s="14">
         <f>'Global Renewables Outlook'!S7*'IEA 2017 Wind'!Z12</f>
         <v>68502.247988834672</v>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="14">
         <f>'Global Renewables Outlook'!T7*'IEA 2017 Wind'!AA12</f>
         <v>73301.743382330329</v>
       </c>
-      <c r="U14" s="15">
+      <c r="U14" s="14">
         <f>'Global Renewables Outlook'!U7*'IEA 2017 Wind'!AB12</f>
         <v>78118.584400074353</v>
       </c>
-      <c r="V14" s="15">
+      <c r="V14" s="14">
         <f>'Global Renewables Outlook'!V7*'IEA 2017 Wind'!AC12</f>
         <v>82951.572348484304</v>
       </c>
-      <c r="W14" s="15">
+      <c r="W14" s="14">
         <f>'Global Renewables Outlook'!W7*'IEA 2017 Wind'!AD12</f>
         <v>87799.616496860792</v>
       </c>
-      <c r="X14" s="15">
+      <c r="X14" s="14">
         <f>'Global Renewables Outlook'!X7*'IEA 2017 Wind'!AE12</f>
         <v>94276.608240385627</v>
       </c>
-      <c r="Y14" s="15">
+      <c r="Y14" s="14">
         <f>'Global Renewables Outlook'!Y7*'IEA 2017 Wind'!AF12</f>
         <v>100789.03999310276</v>
       </c>
-      <c r="Z14" s="15">
+      <c r="Z14" s="14">
         <f>'Global Renewables Outlook'!Z7*'IEA 2017 Wind'!AG12</f>
         <v>107334.83589871647</v>
       </c>
-      <c r="AA14" s="15">
+      <c r="AA14" s="14">
         <f>'Global Renewables Outlook'!AA7*'IEA 2017 Wind'!AH12</f>
         <v>113912.07911727707</v>
       </c>
-      <c r="AB14" s="15">
+      <c r="AB14" s="14">
         <f>'Global Renewables Outlook'!AB7*'IEA 2017 Wind'!AI12</f>
         <v>120518.99688493161</v>
       </c>
-      <c r="AC14" s="15">
+      <c r="AC14" s="14">
         <f>'Global Renewables Outlook'!AC7*'IEA 2017 Wind'!AJ12</f>
         <v>128367.76981657001</v>
       </c>
-      <c r="AD14" s="15">
+      <c r="AD14" s="14">
         <f>'Global Renewables Outlook'!AD7*'IEA 2017 Wind'!AK12</f>
         <v>136155.58022532647</v>
       </c>
-      <c r="AE14" s="15">
+      <c r="AE14" s="14">
         <f>'Global Renewables Outlook'!AE7*'IEA 2017 Wind'!AL12</f>
         <v>143887.26913275797</v>
       </c>
-      <c r="AF14" s="15">
+      <c r="AF14" s="14">
         <f>'Global Renewables Outlook'!AF7*'IEA 2017 Wind'!AM12</f>
         <v>151567.17821208638</v>
       </c>
-      <c r="AG14" s="15">
+      <c r="AG14" s="14">
         <f>'Global Renewables Outlook'!AG7*'IEA 2017 Wind'!AN12</f>
         <v>159199.21255397078</v>
       </c>
+      <c r="AH14">
+        <f>_xlfn.FORECAST.LINEAR(AH1,$B$14:$AG$14,$B$1:$AG$1)</f>
+        <v>145822.22134837136</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" ref="AI14:BA14" si="2">_xlfn.FORECAST.LINEAR(AI1,$B$14:$AG$14,$B$1:$AG$1)</f>
+        <v>150343.86956198141</v>
+      </c>
+      <c r="AJ14">
+        <f t="shared" si="2"/>
+        <v>154865.51777559333</v>
+      </c>
+      <c r="AK14">
+        <f t="shared" si="2"/>
+        <v>159387.16598920338</v>
+      </c>
+      <c r="AL14">
+        <f t="shared" si="2"/>
+        <v>163908.81420281529</v>
+      </c>
+      <c r="AM14">
+        <f t="shared" si="2"/>
+        <v>168430.46241642535</v>
+      </c>
+      <c r="AN14">
+        <f t="shared" si="2"/>
+        <v>172952.1106300354</v>
+      </c>
+      <c r="AO14">
+        <f t="shared" si="2"/>
+        <v>177473.75884364732</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="2"/>
+        <v>181995.40705725737</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" si="2"/>
+        <v>186517.05527086742</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" si="2"/>
+        <v>191038.70348447934</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" si="2"/>
+        <v>195560.35169808939</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" si="2"/>
+        <v>200081.99991170131</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" si="2"/>
+        <v>204603.64812531136</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" si="2"/>
+        <v>209125.29633892141</v>
+      </c>
+      <c r="AW14">
+        <f t="shared" si="2"/>
+        <v>213646.94455253333</v>
+      </c>
+      <c r="AX14">
+        <f t="shared" si="2"/>
+        <v>218168.59276614338</v>
+      </c>
+      <c r="AY14">
+        <f t="shared" si="2"/>
+        <v>222690.24097975343</v>
+      </c>
+      <c r="AZ14">
+        <f t="shared" si="2"/>
+        <v>227211.88919336535</v>
+      </c>
+      <c r="BA14">
+        <f t="shared" si="2"/>
+        <v>231733.5374069754</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>28</v>
       </c>
@@ -4147,8 +5060,68 @@
       <c r="AG15">
         <v>0</v>
       </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -4248,8 +5221,68 @@
       <c r="AG16">
         <v>0</v>
       </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>30</v>
       </c>
@@ -4347,6 +5380,66 @@
         <v>0</v>
       </c>
       <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
         <v>0</v>
       </c>
     </row>
